--- a/Assets/Lion/Minion/GameData/Excel/Minion_2.xlsx
+++ b/Assets/Lion/Minion/GameData/Excel/Minion_2.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Lion\Assets\Lion\Minion\GameData\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A031698A-DB49-4376-AE02-191269695492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD51D990-C85D-4F1C-AA0B-2D567FD6A5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12810" windowWidth="16440" windowHeight="28320" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpLevelStatusTable" sheetId="3" r:id="rId1"/>
-    <sheet name="ItemLevelUpCostTable" sheetId="1" r:id="rId2"/>
-    <sheet name="ItemLevelStatusTable" sheetId="2" r:id="rId3"/>
+    <sheet name="ExpLevelUpCostTable" sheetId="4" r:id="rId1"/>
+    <sheet name="ExpLevelStatusTable" sheetId="3" r:id="rId2"/>
+    <sheet name="ItemLevelUpCostTable" sheetId="1" r:id="rId3"/>
+    <sheet name="ItemLevelStatusTable" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Luck</t>
     <phoneticPr fontId="1"/>
@@ -415,3516 +416,4136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BC1CD1-F6FF-4807-80C4-5A3958CDE1F7}">
+  <dimension ref="A1:B121"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3">
+        <v>6050</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
+        <v>6655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3">
+        <v>7320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>8052</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3">
+        <v>8857</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3">
+        <v>9742</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10716</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3">
+        <v>12965</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3">
+        <v>14261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>15687</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3">
+        <v>17255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3">
+        <v>18980</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3">
+        <v>20878</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3">
+        <v>22965</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3">
+        <v>25261</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3">
+        <v>27787</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3">
+        <v>30565</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3">
+        <v>33621</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3">
+        <v>36983</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3">
+        <v>40681</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3">
+        <v>44749</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3">
+        <v>49223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3">
+        <v>54145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3">
+        <v>59559</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3">
+        <v>65514</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3">
+        <v>72065</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3">
+        <v>79271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3">
+        <v>87198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3">
+        <v>95917</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3">
+        <v>105508</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3">
+        <v>116058</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3">
+        <v>127663</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3">
+        <v>140429</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3">
+        <v>154471</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3">
+        <v>169918</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3">
+        <v>186909</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3">
+        <v>205599</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3">
+        <v>226158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3">
+        <v>248773</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3">
+        <v>273650</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3">
+        <v>301015</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3">
+        <v>331116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3">
+        <v>364227</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3">
+        <v>400649</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3">
+        <v>440713</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3">
+        <v>484784</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3">
+        <v>533262</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3">
+        <v>586588</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3">
+        <v>645246</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3">
+        <v>709770</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3">
+        <v>780747</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3">
+        <v>858821</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3">
+        <v>944703</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1039173</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1143090</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1257399</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1383138</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1521451</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="4">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1673596</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1840955</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2025050</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3">
+        <v>2227555</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2450310</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3">
+        <v>2695341</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2964875</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="4">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3">
+        <v>3261362</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3">
+        <v>3587498</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3">
+        <v>3946247</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="4">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3">
+        <v>4340871</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3">
+        <v>4774958</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3">
+        <v>5252453</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="4">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3">
+        <v>5777698</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3">
+        <v>6355467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3">
+        <v>6991013</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="4">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3">
+        <v>7690114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3">
+        <v>8459125</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3">
+        <v>9305037</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="4">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3">
+        <v>10235540</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3">
+        <v>11259094</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3">
+        <v>12385003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="4">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3">
+        <v>13623503</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3">
+        <v>14985853</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3">
+        <v>16484438</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="4">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3">
+        <v>18132881</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3">
+        <v>19946169</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3">
+        <v>21940785</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3">
+        <v>24134863</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="4">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3">
+        <v>26548349</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3">
+        <v>29203183</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3">
+        <v>32123501</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="4">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3">
+        <v>35335851</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3">
+        <v>38869436</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="3">
+        <v>42756379</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="4">
+        <v>118</v>
+      </c>
+      <c r="B119" s="3">
+        <v>47032016</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3">
+        <v>51735217</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="3">
+        <v>56908738</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A588501A-B26D-415D-8244-EA21C69E46CA}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" s="3">
+        <v>100</v>
       </c>
       <c r="C2" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>10</v>
+      <c r="B3" s="3">
+        <v>102</v>
       </c>
       <c r="C3" s="3">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D3" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3">
         <v>1.05</v>
       </c>
+      <c r="G3">
+        <v>3.3</v>
+      </c>
       <c r="H3">
-        <v>3.3</v>
-      </c>
-      <c r="I3">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>20</v>
+      <c r="B4" s="3">
+        <v>105</v>
       </c>
       <c r="C4" s="3">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D4" s="3">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3">
         <v>1.1000000000000001</v>
       </c>
+      <c r="G4">
+        <v>3.6</v>
+      </c>
       <c r="H4">
-        <v>3.6</v>
-      </c>
-      <c r="I4">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>30</v>
+      <c r="B5" s="3">
+        <v>110</v>
       </c>
       <c r="C5" s="3">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3">
         <v>1.1499999999999999</v>
       </c>
+      <c r="G5">
+        <v>3.9</v>
+      </c>
       <c r="H5">
-        <v>3.9</v>
-      </c>
-      <c r="I5">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:8">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>40</v>
+      <c r="B6" s="3">
+        <v>115</v>
       </c>
       <c r="C6" s="3">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D6" s="3">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3">
         <v>1.2</v>
       </c>
+      <c r="G6">
+        <v>4.2</v>
+      </c>
       <c r="H6">
-        <v>4.2</v>
-      </c>
-      <c r="I6">
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>50</v>
+      <c r="B7" s="3">
+        <v>120</v>
       </c>
       <c r="C7" s="3">
-        <v>120</v>
+        <v>77.3</v>
       </c>
       <c r="D7" s="3">
-        <v>77.3</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="E7" s="3">
-        <v>33.799999999999997</v>
+        <v>22.8</v>
       </c>
       <c r="F7" s="3">
-        <v>22.8</v>
-      </c>
-      <c r="G7" s="3">
         <v>1.25</v>
       </c>
+      <c r="G7">
+        <v>4.5</v>
+      </c>
       <c r="H7">
-        <v>4.5</v>
-      </c>
-      <c r="I7">
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>80</v>
+      <c r="B8" s="3">
+        <v>130</v>
       </c>
       <c r="C8" s="3">
-        <v>130</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="D8" s="3">
-        <v>80.599999999999994</v>
+        <v>37.6</v>
       </c>
       <c r="E8" s="3">
-        <v>37.6</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3">
         <v>1.3</v>
       </c>
+      <c r="G8">
+        <v>4.8</v>
+      </c>
       <c r="H8">
-        <v>4.8</v>
-      </c>
-      <c r="I8">
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:8">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>120</v>
+      <c r="B9" s="3">
+        <v>140</v>
       </c>
       <c r="C9" s="3">
-        <v>140</v>
+        <v>83.9</v>
       </c>
       <c r="D9" s="3">
-        <v>83.9</v>
+        <v>41.4</v>
       </c>
       <c r="E9" s="3">
-        <v>41.4</v>
+        <v>27.2</v>
       </c>
       <c r="F9" s="3">
-        <v>27.2</v>
-      </c>
-      <c r="G9" s="3">
         <v>1.4</v>
       </c>
+      <c r="G9">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="H9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I9">
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>200</v>
+      <c r="B10" s="3">
+        <v>150</v>
       </c>
       <c r="C10" s="3">
-        <v>150</v>
+        <v>87.2</v>
       </c>
       <c r="D10" s="3">
-        <v>87.2</v>
+        <v>45.2</v>
       </c>
       <c r="E10" s="3">
-        <v>45.2</v>
+        <v>29.4</v>
       </c>
       <c r="F10" s="3">
-        <v>29.4</v>
-      </c>
-      <c r="G10" s="3">
         <v>1.5</v>
       </c>
+      <c r="G10">
+        <v>5.4</v>
+      </c>
       <c r="H10">
-        <v>5.4</v>
-      </c>
-      <c r="I10">
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>300</v>
+      <c r="B11" s="3">
+        <v>160</v>
       </c>
       <c r="C11" s="3">
-        <v>160</v>
+        <v>90.5</v>
       </c>
       <c r="D11" s="3">
-        <v>90.5</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3">
-        <v>49</v>
+        <v>31.6</v>
       </c>
       <c r="F11" s="3">
-        <v>31.6</v>
-      </c>
-      <c r="G11" s="3">
         <v>1.75</v>
       </c>
+      <c r="G11">
+        <v>5.7</v>
+      </c>
       <c r="H11">
-        <v>5.7</v>
-      </c>
-      <c r="I11">
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:8">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>500</v>
+      <c r="B12" s="3">
+        <v>170</v>
       </c>
       <c r="C12" s="3">
-        <v>170</v>
+        <v>93.8</v>
       </c>
       <c r="D12" s="3">
-        <v>93.8</v>
+        <v>52.8</v>
       </c>
       <c r="E12" s="3">
-        <v>52.8</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="F12" s="3">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="G12" s="3">
         <v>2</v>
       </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
       <c r="H12">
-        <v>6</v>
-      </c>
-      <c r="I12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>700</v>
+      <c r="B13" s="3">
+        <v>180</v>
       </c>
       <c r="C13" s="3">
-        <v>180</v>
+        <v>97.1</v>
       </c>
       <c r="D13" s="3">
-        <v>97.1</v>
+        <v>56.6</v>
       </c>
       <c r="E13" s="3">
-        <v>56.6</v>
+        <v>36</v>
       </c>
       <c r="F13" s="3">
-        <v>36</v>
-      </c>
-      <c r="G13" s="3">
         <v>2.5</v>
       </c>
+      <c r="G13">
+        <v>6.3</v>
+      </c>
       <c r="H13">
-        <v>6.3</v>
-      </c>
-      <c r="I13">
         <v>2.1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>900</v>
+      <c r="B14" s="3">
+        <v>190</v>
       </c>
       <c r="C14" s="3">
-        <v>190</v>
+        <v>100.4</v>
       </c>
       <c r="D14" s="3">
-        <v>100.4</v>
+        <v>60.4</v>
       </c>
       <c r="E14" s="3">
-        <v>60.4</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="F14" s="3">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="G14" s="3">
         <v>3</v>
       </c>
+      <c r="G14">
+        <v>6.6</v>
+      </c>
       <c r="H14">
-        <v>6.6</v>
-      </c>
-      <c r="I14">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:8">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>1200</v>
+      <c r="B15" s="3">
+        <v>200</v>
       </c>
       <c r="C15" s="3">
-        <v>200</v>
+        <v>103.7</v>
       </c>
       <c r="D15" s="3">
-        <v>103.7</v>
+        <v>64.2</v>
       </c>
       <c r="E15" s="3">
-        <v>64.2</v>
+        <v>40.4</v>
       </c>
       <c r="F15" s="3">
-        <v>40.4</v>
-      </c>
-      <c r="G15" s="3">
         <v>3.5</v>
       </c>
+      <c r="G15">
+        <v>6.9</v>
+      </c>
       <c r="H15">
-        <v>6.9</v>
-      </c>
-      <c r="I15">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>1500</v>
+      <c r="B16" s="3">
+        <v>220</v>
       </c>
       <c r="C16" s="3">
-        <v>220</v>
+        <v>107</v>
       </c>
       <c r="D16" s="3">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3">
-        <v>68</v>
+        <v>42.6</v>
       </c>
       <c r="F16" s="3">
-        <v>42.6</v>
-      </c>
-      <c r="G16" s="3">
         <v>4</v>
       </c>
+      <c r="G16">
+        <v>7.2</v>
+      </c>
       <c r="H16">
-        <v>7.2</v>
-      </c>
-      <c r="I16">
         <v>2.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>2000</v>
+      <c r="B17" s="3">
+        <v>240</v>
       </c>
       <c r="C17" s="3">
-        <v>240</v>
+        <v>110.3</v>
       </c>
       <c r="D17" s="3">
-        <v>110.3</v>
+        <v>71.8</v>
       </c>
       <c r="E17" s="3">
-        <v>71.8</v>
+        <v>44.8</v>
       </c>
       <c r="F17" s="3">
-        <v>44.8</v>
-      </c>
-      <c r="G17" s="3">
         <v>4.5</v>
       </c>
+      <c r="G17">
+        <v>7.5</v>
+      </c>
       <c r="H17">
-        <v>7.5</v>
-      </c>
-      <c r="I17">
         <v>2.5</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:8">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>2500</v>
+      <c r="B18" s="3">
+        <v>260</v>
       </c>
       <c r="C18" s="3">
-        <v>260</v>
+        <v>113.6</v>
       </c>
       <c r="D18" s="3">
-        <v>113.6</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="E18" s="3">
-        <v>75.599999999999994</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
-      </c>
-      <c r="G18" s="3">
         <v>5</v>
       </c>
+      <c r="G18">
+        <v>7.8</v>
+      </c>
       <c r="H18">
-        <v>7.8</v>
-      </c>
-      <c r="I18">
         <v>2.6</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>3000</v>
+      <c r="B19" s="3">
+        <v>280</v>
       </c>
       <c r="C19" s="3">
-        <v>280</v>
+        <v>116.9</v>
       </c>
       <c r="D19" s="3">
-        <v>116.9</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="E19" s="3">
-        <v>79.400000000000006</v>
+        <v>49.2</v>
       </c>
       <c r="F19" s="3">
-        <v>49.2</v>
-      </c>
-      <c r="G19" s="3">
         <v>6</v>
       </c>
+      <c r="G19">
+        <v>8.1</v>
+      </c>
       <c r="H19">
-        <v>8.1</v>
-      </c>
-      <c r="I19">
         <v>2.7</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>3500</v>
+      <c r="B20" s="3">
+        <v>300</v>
       </c>
       <c r="C20" s="3">
-        <v>300</v>
+        <v>120.2</v>
       </c>
       <c r="D20" s="3">
-        <v>120.2</v>
+        <v>83.2</v>
       </c>
       <c r="E20" s="3">
-        <v>83.2</v>
+        <v>51.4</v>
       </c>
       <c r="F20" s="3">
-        <v>51.4</v>
-      </c>
-      <c r="G20" s="3">
         <v>7</v>
       </c>
+      <c r="G20">
+        <v>8.4</v>
+      </c>
       <c r="H20">
-        <v>8.4</v>
-      </c>
-      <c r="I20">
         <v>2.8</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:8">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>4000</v>
+      <c r="B21" s="3">
+        <v>330</v>
       </c>
       <c r="C21" s="3">
-        <v>330</v>
+        <v>123.5</v>
       </c>
       <c r="D21" s="3">
-        <v>123.5</v>
+        <v>87</v>
       </c>
       <c r="E21" s="3">
-        <v>87</v>
+        <v>53.6</v>
       </c>
       <c r="F21" s="3">
-        <v>53.6</v>
-      </c>
-      <c r="G21" s="3">
         <v>8</v>
       </c>
+      <c r="G21">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="H21">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I21">
         <v>2.9</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>4500</v>
+      <c r="B22" s="3">
+        <v>360</v>
       </c>
       <c r="C22" s="3">
-        <v>360</v>
+        <v>126.8</v>
       </c>
       <c r="D22" s="3">
-        <v>126.8</v>
+        <v>90.8</v>
       </c>
       <c r="E22" s="3">
-        <v>90.8</v>
+        <v>55.8</v>
       </c>
       <c r="F22" s="3">
-        <v>55.8</v>
-      </c>
-      <c r="G22" s="3">
         <v>9</v>
       </c>
+      <c r="G22">
+        <v>9</v>
+      </c>
       <c r="H22">
-        <v>9</v>
-      </c>
-      <c r="I22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>5000</v>
+      <c r="B23" s="3">
+        <v>400</v>
       </c>
       <c r="C23" s="3">
-        <v>400</v>
+        <v>130.1</v>
       </c>
       <c r="D23" s="3">
-        <v>130.1</v>
+        <v>94.6</v>
       </c>
       <c r="E23" s="3">
-        <v>94.6</v>
+        <v>58</v>
       </c>
       <c r="F23" s="3">
-        <v>58</v>
-      </c>
-      <c r="G23" s="3">
         <v>10</v>
       </c>
+      <c r="G23">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="H23">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="I23">
         <v>3.1</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>5500</v>
+        <v>420</v>
       </c>
       <c r="C24" s="3">
-        <v>420</v>
+        <v>133.4</v>
       </c>
       <c r="D24" s="3">
-        <v>133.4</v>
+        <v>98.4</v>
       </c>
       <c r="E24" s="3">
-        <v>98.4</v>
+        <v>60.2</v>
       </c>
       <c r="F24" s="3">
-        <v>60.2</v>
-      </c>
-      <c r="G24" s="3">
         <v>10.5</v>
       </c>
+      <c r="G24">
+        <v>9.6</v>
+      </c>
       <c r="H24">
-        <v>9.6</v>
-      </c>
-      <c r="I24">
         <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:8">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>6050</v>
+        <v>440</v>
       </c>
       <c r="C25" s="3">
-        <v>440</v>
+        <v>136.69999999999999</v>
       </c>
       <c r="D25" s="3">
-        <v>136.69999999999999</v>
+        <v>102.2</v>
       </c>
       <c r="E25" s="3">
-        <v>102.2</v>
+        <v>62.4</v>
       </c>
       <c r="F25" s="3">
-        <v>62.4</v>
-      </c>
-      <c r="G25" s="3">
         <v>11</v>
       </c>
+      <c r="G25">
+        <v>9.9</v>
+      </c>
       <c r="H25">
-        <v>9.9</v>
-      </c>
-      <c r="I25">
         <v>3.3</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>6655</v>
+        <v>460</v>
       </c>
       <c r="C26" s="3">
-        <v>460</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="E26" s="3">
-        <v>106</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="F26" s="3">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="G26" s="3">
         <v>11.5</v>
       </c>
+      <c r="G26">
+        <v>10.199999999999999</v>
+      </c>
       <c r="H26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="I26">
         <v>3.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>7320</v>
+        <v>480</v>
       </c>
       <c r="C27" s="3">
-        <v>480</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="D27" s="3">
-        <v>143.30000000000001</v>
+        <v>109.8</v>
       </c>
       <c r="E27" s="3">
-        <v>109.8</v>
+        <v>66.8</v>
       </c>
       <c r="F27" s="3">
-        <v>66.8</v>
-      </c>
-      <c r="G27" s="3">
         <v>12</v>
       </c>
+      <c r="G27">
+        <v>10.5</v>
+      </c>
       <c r="H27">
-        <v>10.5</v>
-      </c>
-      <c r="I27">
         <v>3.5</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:8">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>8052</v>
+        <v>500</v>
       </c>
       <c r="C28" s="3">
-        <v>500</v>
+        <v>146.6</v>
       </c>
       <c r="D28" s="3">
-        <v>146.6</v>
+        <v>113.6</v>
       </c>
       <c r="E28" s="3">
-        <v>113.6</v>
+        <v>69</v>
       </c>
       <c r="F28" s="3">
-        <v>69</v>
-      </c>
-      <c r="G28" s="3">
         <v>12.5</v>
       </c>
+      <c r="G28">
+        <v>10.8</v>
+      </c>
       <c r="H28">
-        <v>10.8</v>
-      </c>
-      <c r="I28">
         <v>3.6</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>8857</v>
+        <v>520</v>
       </c>
       <c r="C29" s="3">
-        <v>520</v>
+        <v>149.9</v>
       </c>
       <c r="D29" s="3">
-        <v>149.9</v>
+        <v>117.4</v>
       </c>
       <c r="E29" s="3">
-        <v>117.4</v>
+        <v>71.2</v>
       </c>
       <c r="F29" s="3">
-        <v>71.2</v>
-      </c>
-      <c r="G29" s="3">
         <v>13</v>
       </c>
+      <c r="G29">
+        <v>11.1</v>
+      </c>
       <c r="H29">
-        <v>11.1</v>
-      </c>
-      <c r="I29">
         <v>3.7</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>9742</v>
+        <v>540</v>
       </c>
       <c r="C30" s="3">
-        <v>540</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="D30" s="3">
-        <v>153.19999999999999</v>
+        <v>121.2</v>
       </c>
       <c r="E30" s="3">
-        <v>121.2</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="F30" s="3">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="G30" s="3">
         <v>13.5</v>
       </c>
+      <c r="G30">
+        <v>11.4</v>
+      </c>
       <c r="H30">
-        <v>11.4</v>
-      </c>
-      <c r="I30">
         <v>3.8</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>10716</v>
+        <v>560</v>
       </c>
       <c r="C31" s="3">
-        <v>560</v>
+        <v>156.5</v>
       </c>
       <c r="D31" s="3">
-        <v>156.5</v>
+        <v>125</v>
       </c>
       <c r="E31" s="3">
-        <v>125</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="F31" s="3">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="G31" s="3">
         <v>14</v>
       </c>
+      <c r="G31">
+        <v>11.7</v>
+      </c>
       <c r="H31">
-        <v>11.7</v>
-      </c>
-      <c r="I31">
         <v>3.9</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>11787</v>
+        <v>580</v>
       </c>
       <c r="C32" s="3">
-        <v>580</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="D32" s="3">
-        <v>159.80000000000001</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="E32" s="3">
-        <v>128.80000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="F32" s="3">
-        <v>77.8</v>
-      </c>
-      <c r="G32" s="3">
         <v>14.5</v>
       </c>
+      <c r="G32">
+        <v>12</v>
+      </c>
       <c r="H32">
-        <v>12</v>
-      </c>
-      <c r="I32">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>12965</v>
+        <v>600</v>
       </c>
       <c r="C33" s="3">
-        <v>600</v>
+        <v>163.1</v>
       </c>
       <c r="D33" s="3">
-        <v>163.1</v>
+        <v>132.6</v>
       </c>
       <c r="E33" s="3">
-        <v>132.6</v>
+        <v>80</v>
       </c>
       <c r="F33" s="3">
-        <v>80</v>
-      </c>
-      <c r="G33" s="3">
         <v>15</v>
       </c>
+      <c r="G33">
+        <v>12.3</v>
+      </c>
       <c r="H33">
-        <v>12.3</v>
-      </c>
-      <c r="I33">
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:8">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>14261</v>
+        <v>620</v>
       </c>
       <c r="C34" s="3">
-        <v>620</v>
+        <v>166.4</v>
       </c>
       <c r="D34" s="3">
-        <v>166.4</v>
+        <v>136.4</v>
       </c>
       <c r="E34" s="3">
-        <v>136.4</v>
+        <v>82.2</v>
       </c>
       <c r="F34" s="3">
-        <v>82.2</v>
-      </c>
-      <c r="G34" s="3">
         <v>15.5</v>
       </c>
+      <c r="G34">
+        <v>12.6</v>
+      </c>
       <c r="H34">
-        <v>12.6</v>
-      </c>
-      <c r="I34">
         <v>4.2</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>15687</v>
+        <v>640</v>
       </c>
       <c r="C35" s="3">
-        <v>640</v>
+        <v>169.7</v>
       </c>
       <c r="D35" s="3">
-        <v>169.7</v>
+        <v>140.19999999999999</v>
       </c>
       <c r="E35" s="3">
-        <v>140.19999999999999</v>
+        <v>84.4</v>
       </c>
       <c r="F35" s="3">
-        <v>84.4</v>
-      </c>
-      <c r="G35" s="3">
         <v>16</v>
       </c>
+      <c r="G35">
+        <v>12.9</v>
+      </c>
       <c r="H35">
-        <v>12.9</v>
-      </c>
-      <c r="I35">
         <v>4.3</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>17255</v>
+        <v>660</v>
       </c>
       <c r="C36" s="3">
-        <v>660</v>
+        <v>173</v>
       </c>
       <c r="D36" s="3">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="E36" s="3">
-        <v>144</v>
+        <v>86.6</v>
       </c>
       <c r="F36" s="3">
-        <v>86.6</v>
-      </c>
-      <c r="G36" s="3">
         <v>16.5</v>
       </c>
+      <c r="G36">
+        <v>13.2</v>
+      </c>
       <c r="H36">
-        <v>13.2</v>
-      </c>
-      <c r="I36">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:8">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="3">
-        <v>18980</v>
+        <v>680</v>
       </c>
       <c r="C37" s="3">
-        <v>680</v>
+        <v>176.3</v>
       </c>
       <c r="D37" s="3">
-        <v>176.3</v>
+        <v>147.80000000000001</v>
       </c>
       <c r="E37" s="3">
-        <v>147.80000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="F37" s="3">
-        <v>88.8</v>
-      </c>
-      <c r="G37" s="3">
         <v>17</v>
       </c>
+      <c r="G37">
+        <v>13.5</v>
+      </c>
       <c r="H37">
-        <v>13.5</v>
-      </c>
-      <c r="I37">
         <v>4.5</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="3">
-        <v>20878</v>
+        <v>700</v>
       </c>
       <c r="C38" s="3">
-        <v>700</v>
+        <v>179.6</v>
       </c>
       <c r="D38" s="3">
-        <v>179.6</v>
+        <v>151.6</v>
       </c>
       <c r="E38" s="3">
-        <v>151.6</v>
+        <v>91</v>
       </c>
       <c r="F38" s="3">
-        <v>91</v>
-      </c>
-      <c r="G38" s="3">
         <v>17.5</v>
       </c>
+      <c r="G38">
+        <v>13.8</v>
+      </c>
       <c r="H38">
-        <v>13.8</v>
-      </c>
-      <c r="I38">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="3">
-        <v>22965</v>
+        <v>720</v>
       </c>
       <c r="C39" s="3">
-        <v>720</v>
+        <v>182.9</v>
       </c>
       <c r="D39" s="3">
-        <v>182.9</v>
+        <v>155.4</v>
       </c>
       <c r="E39" s="3">
-        <v>155.4</v>
+        <v>93.2</v>
       </c>
       <c r="F39" s="3">
-        <v>93.2</v>
-      </c>
-      <c r="G39" s="3">
         <v>18</v>
       </c>
+      <c r="G39">
+        <v>14.1</v>
+      </c>
       <c r="H39">
-        <v>14.1</v>
-      </c>
-      <c r="I39">
         <v>4.7</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:8">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="3">
-        <v>25261</v>
+        <v>740</v>
       </c>
       <c r="C40" s="3">
-        <v>740</v>
+        <v>186.2</v>
       </c>
       <c r="D40" s="3">
-        <v>186.2</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="E40" s="3">
-        <v>159.19999999999999</v>
+        <v>95.4</v>
       </c>
       <c r="F40" s="3">
-        <v>95.4</v>
-      </c>
-      <c r="G40" s="3">
         <v>18.5</v>
       </c>
+      <c r="G40">
+        <v>14.4</v>
+      </c>
       <c r="H40">
-        <v>14.4</v>
-      </c>
-      <c r="I40">
         <v>4.8</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="3">
-        <v>27787</v>
+        <v>760</v>
       </c>
       <c r="C41" s="3">
-        <v>760</v>
+        <v>189.5</v>
       </c>
       <c r="D41" s="3">
-        <v>189.5</v>
+        <v>163</v>
       </c>
       <c r="E41" s="3">
-        <v>163</v>
+        <v>97.6</v>
       </c>
       <c r="F41" s="3">
-        <v>97.6</v>
-      </c>
-      <c r="G41" s="3">
         <v>19</v>
       </c>
+      <c r="G41">
+        <v>14.7</v>
+      </c>
       <c r="H41">
-        <v>14.7</v>
-      </c>
-      <c r="I41">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>30565</v>
+        <v>780</v>
       </c>
       <c r="C42" s="3">
-        <v>780</v>
+        <v>192.8</v>
       </c>
       <c r="D42" s="3">
-        <v>192.8</v>
+        <v>166.8</v>
       </c>
       <c r="E42" s="3">
-        <v>166.8</v>
+        <v>99.8</v>
       </c>
       <c r="F42" s="3">
-        <v>99.8</v>
-      </c>
-      <c r="G42" s="3">
         <v>19.5</v>
       </c>
+      <c r="G42">
+        <v>15</v>
+      </c>
       <c r="H42">
-        <v>15</v>
-      </c>
-      <c r="I42">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:8">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="3">
-        <v>33621</v>
+        <v>800</v>
       </c>
       <c r="C43" s="3">
-        <v>800</v>
+        <v>196.1</v>
       </c>
       <c r="D43" s="3">
-        <v>196.1</v>
+        <v>170.6</v>
       </c>
       <c r="E43" s="3">
-        <v>170.6</v>
+        <v>102</v>
       </c>
       <c r="F43" s="3">
-        <v>102</v>
-      </c>
-      <c r="G43" s="3">
         <v>20</v>
       </c>
+      <c r="G43">
+        <v>15.3</v>
+      </c>
       <c r="H43">
-        <v>15.3</v>
-      </c>
-      <c r="I43">
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>36983</v>
+        <v>820</v>
       </c>
       <c r="C44" s="3">
-        <v>820</v>
+        <v>199.4</v>
       </c>
       <c r="D44" s="3">
-        <v>199.4</v>
+        <v>174.4</v>
       </c>
       <c r="E44" s="3">
-        <v>174.4</v>
+        <v>104.2</v>
       </c>
       <c r="F44" s="3">
-        <v>104.2</v>
-      </c>
-      <c r="G44" s="3">
         <v>20.5</v>
       </c>
+      <c r="G44">
+        <v>15.6</v>
+      </c>
       <c r="H44">
-        <v>15.6</v>
-      </c>
-      <c r="I44">
         <v>5.2</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="3">
-        <v>40681</v>
+        <v>840</v>
       </c>
       <c r="C45" s="3">
-        <v>840</v>
+        <v>202.7</v>
       </c>
       <c r="D45" s="3">
-        <v>202.7</v>
+        <v>178.2</v>
       </c>
       <c r="E45" s="3">
-        <v>178.2</v>
+        <v>106.4</v>
       </c>
       <c r="F45" s="3">
-        <v>106.4</v>
-      </c>
-      <c r="G45" s="3">
         <v>21</v>
       </c>
+      <c r="G45">
+        <v>15.9</v>
+      </c>
       <c r="H45">
-        <v>15.9</v>
-      </c>
-      <c r="I45">
         <v>5.3</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>44749</v>
+        <v>860</v>
       </c>
       <c r="C46" s="3">
-        <v>860</v>
+        <v>206</v>
       </c>
       <c r="D46" s="3">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E46" s="3">
-        <v>182</v>
+        <v>108.6</v>
       </c>
       <c r="F46" s="3">
-        <v>108.6</v>
-      </c>
-      <c r="G46" s="3">
         <v>21.5</v>
       </c>
+      <c r="G46">
+        <v>16.2</v>
+      </c>
       <c r="H46">
-        <v>16.2</v>
-      </c>
-      <c r="I46">
         <v>5.4</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:8">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="3">
-        <v>49223</v>
+        <v>880</v>
       </c>
       <c r="C47" s="3">
-        <v>880</v>
+        <v>209.3</v>
       </c>
       <c r="D47" s="3">
-        <v>209.3</v>
+        <v>185.8</v>
       </c>
       <c r="E47" s="3">
-        <v>185.8</v>
+        <v>110.8</v>
       </c>
       <c r="F47" s="3">
-        <v>110.8</v>
-      </c>
-      <c r="G47" s="3">
         <v>22</v>
       </c>
+      <c r="G47">
+        <v>16.5</v>
+      </c>
       <c r="H47">
-        <v>16.5</v>
-      </c>
-      <c r="I47">
         <v>5.5</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="3">
-        <v>54145</v>
+        <v>900</v>
       </c>
       <c r="C48" s="3">
-        <v>900</v>
+        <v>212.6</v>
       </c>
       <c r="D48" s="3">
-        <v>212.6</v>
+        <v>189.6</v>
       </c>
       <c r="E48" s="3">
-        <v>189.6</v>
+        <v>113</v>
       </c>
       <c r="F48" s="3">
-        <v>113</v>
-      </c>
-      <c r="G48" s="3">
         <v>22.5</v>
       </c>
+      <c r="G48">
+        <v>16.8</v>
+      </c>
       <c r="H48">
-        <v>16.8</v>
-      </c>
-      <c r="I48">
         <v>5.6</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="3">
-        <v>59559</v>
+        <v>920</v>
       </c>
       <c r="C49" s="3">
-        <v>920</v>
+        <v>215.9</v>
       </c>
       <c r="D49" s="3">
-        <v>215.9</v>
+        <v>193.4</v>
       </c>
       <c r="E49" s="3">
-        <v>193.4</v>
+        <v>115.2</v>
       </c>
       <c r="F49" s="3">
-        <v>115.2</v>
-      </c>
-      <c r="G49" s="3">
         <v>23</v>
       </c>
+      <c r="G49">
+        <v>17.100000000000001</v>
+      </c>
       <c r="H49">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="I49">
         <v>5.7</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:8">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="3">
-        <v>65514</v>
+        <v>940</v>
       </c>
       <c r="C50" s="3">
-        <v>940</v>
+        <v>219.2</v>
       </c>
       <c r="D50" s="3">
-        <v>219.2</v>
+        <v>197.2</v>
       </c>
       <c r="E50" s="3">
-        <v>197.2</v>
+        <v>117.4</v>
       </c>
       <c r="F50" s="3">
-        <v>117.4</v>
-      </c>
-      <c r="G50" s="3">
         <v>23.5</v>
       </c>
+      <c r="G50">
+        <v>17.399999999999999</v>
+      </c>
       <c r="H50">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="I50">
         <v>5.8</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="3">
-        <v>72065</v>
+        <v>960</v>
       </c>
       <c r="C51" s="3">
-        <v>960</v>
+        <v>222.5</v>
       </c>
       <c r="D51" s="3">
-        <v>222.5</v>
+        <v>201</v>
       </c>
       <c r="E51" s="3">
-        <v>201</v>
+        <v>119.6</v>
       </c>
       <c r="F51" s="3">
-        <v>119.6</v>
-      </c>
-      <c r="G51" s="3">
         <v>24</v>
       </c>
+      <c r="G51">
+        <v>17.7</v>
+      </c>
       <c r="H51">
-        <v>17.7</v>
-      </c>
-      <c r="I51">
         <v>5.9</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>79271</v>
+        <v>980</v>
       </c>
       <c r="C52" s="3">
-        <v>980</v>
+        <v>225.8</v>
       </c>
       <c r="D52" s="3">
-        <v>225.8</v>
+        <v>204.8</v>
       </c>
       <c r="E52" s="3">
-        <v>204.8</v>
+        <v>121.8</v>
       </c>
       <c r="F52" s="3">
-        <v>121.8</v>
-      </c>
-      <c r="G52" s="3">
         <v>24.5</v>
       </c>
+      <c r="G52">
+        <v>18</v>
+      </c>
       <c r="H52">
-        <v>18</v>
-      </c>
-      <c r="I52">
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:8">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="3">
-        <v>87198</v>
+        <v>1000</v>
       </c>
       <c r="C53" s="3">
-        <v>1000</v>
+        <v>229.1</v>
       </c>
       <c r="D53" s="3">
-        <v>229.1</v>
+        <v>208.6</v>
       </c>
       <c r="E53" s="3">
-        <v>208.6</v>
+        <v>124</v>
       </c>
       <c r="F53" s="3">
-        <v>124</v>
-      </c>
-      <c r="G53" s="3">
         <v>25</v>
       </c>
+      <c r="G53">
+        <v>18.3</v>
+      </c>
       <c r="H53">
-        <v>18.3</v>
-      </c>
-      <c r="I53">
         <v>6.1</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>95917</v>
+        <v>1020</v>
       </c>
       <c r="C54" s="3">
-        <v>1020</v>
+        <v>232.4</v>
       </c>
       <c r="D54" s="3">
-        <v>232.4</v>
+        <v>212.4</v>
       </c>
       <c r="E54" s="3">
-        <v>212.4</v>
+        <v>126.2</v>
       </c>
       <c r="F54" s="3">
-        <v>126.2</v>
-      </c>
-      <c r="G54" s="3">
         <v>25.5</v>
       </c>
+      <c r="G54">
+        <v>18.600000000000001</v>
+      </c>
       <c r="H54">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="I54">
         <v>6.2</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="3">
-        <v>105508</v>
+        <v>1040</v>
       </c>
       <c r="C55" s="3">
-        <v>1040</v>
+        <v>235.7</v>
       </c>
       <c r="D55" s="3">
-        <v>235.7</v>
+        <v>216.2</v>
       </c>
       <c r="E55" s="3">
-        <v>216.2</v>
+        <v>128.4</v>
       </c>
       <c r="F55" s="3">
-        <v>128.4</v>
-      </c>
-      <c r="G55" s="3">
         <v>26</v>
       </c>
+      <c r="G55">
+        <v>18.899999999999999</v>
+      </c>
       <c r="H55">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="I55">
         <v>6.3</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:8">
       <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>116058</v>
+        <v>1060</v>
       </c>
       <c r="C56" s="3">
-        <v>1060</v>
+        <v>239</v>
       </c>
       <c r="D56" s="3">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E56" s="3">
-        <v>220</v>
+        <v>130.6</v>
       </c>
       <c r="F56" s="3">
-        <v>130.6</v>
-      </c>
-      <c r="G56" s="3">
         <v>26.5</v>
       </c>
+      <c r="G56">
+        <v>19.2</v>
+      </c>
       <c r="H56">
-        <v>19.2</v>
-      </c>
-      <c r="I56">
         <v>6.4</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="3">
-        <v>127663</v>
+        <v>1080</v>
       </c>
       <c r="C57" s="3">
-        <v>1080</v>
+        <v>242.3</v>
       </c>
       <c r="D57" s="3">
-        <v>242.3</v>
+        <v>223.8</v>
       </c>
       <c r="E57" s="3">
-        <v>223.8</v>
+        <v>132.80000000000001</v>
       </c>
       <c r="F57" s="3">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="G57" s="3">
         <v>27</v>
       </c>
+      <c r="G57">
+        <v>19.5</v>
+      </c>
       <c r="H57">
-        <v>19.5</v>
-      </c>
-      <c r="I57">
         <v>6.5000000000000098</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>140429</v>
+        <v>1100</v>
       </c>
       <c r="C58" s="3">
-        <v>1100</v>
+        <v>245.6</v>
       </c>
       <c r="D58" s="3">
-        <v>245.6</v>
+        <v>227.6</v>
       </c>
       <c r="E58" s="3">
-        <v>227.6</v>
+        <v>135</v>
       </c>
       <c r="F58" s="3">
-        <v>135</v>
-      </c>
-      <c r="G58" s="3">
         <v>27.5</v>
       </c>
+      <c r="G58">
+        <v>19.8</v>
+      </c>
       <c r="H58">
-        <v>19.8</v>
-      </c>
-      <c r="I58">
         <v>6.6</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:8">
       <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="3">
-        <v>154471</v>
+        <v>1120</v>
       </c>
       <c r="C59" s="3">
-        <v>1120</v>
+        <v>248.9</v>
       </c>
       <c r="D59" s="3">
-        <v>248.9</v>
+        <v>231.4</v>
       </c>
       <c r="E59" s="3">
-        <v>231.4</v>
+        <v>137.19999999999999</v>
       </c>
       <c r="F59" s="3">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="G59" s="3">
         <v>28</v>
       </c>
+      <c r="G59">
+        <v>20.100000000000001</v>
+      </c>
       <c r="H59">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="I59">
         <v>6.7</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>169918</v>
+        <v>1140</v>
       </c>
       <c r="C60" s="3">
-        <v>1140</v>
+        <v>252.2</v>
       </c>
       <c r="D60" s="3">
-        <v>252.2</v>
+        <v>235.2</v>
       </c>
       <c r="E60" s="3">
-        <v>235.2</v>
+        <v>139.4</v>
       </c>
       <c r="F60" s="3">
-        <v>139.4</v>
-      </c>
-      <c r="G60" s="3">
         <v>28.5</v>
       </c>
+      <c r="G60">
+        <v>20.399999999999999</v>
+      </c>
       <c r="H60">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="I60">
         <v>6.8000000000000096</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" s="3">
-        <v>186909</v>
+        <v>1160</v>
       </c>
       <c r="C61" s="3">
-        <v>1160</v>
+        <v>255.5</v>
       </c>
       <c r="D61" s="3">
-        <v>255.5</v>
+        <v>239</v>
       </c>
       <c r="E61" s="3">
-        <v>239</v>
+        <v>141.6</v>
       </c>
       <c r="F61" s="3">
-        <v>141.6</v>
-      </c>
-      <c r="G61" s="3">
         <v>29</v>
       </c>
+      <c r="G61">
+        <v>20.7</v>
+      </c>
       <c r="H61">
-        <v>20.7</v>
-      </c>
-      <c r="I61">
         <v>6.9000000000000101</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:8">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>205599</v>
+        <v>1180</v>
       </c>
       <c r="C62" s="3">
-        <v>1180</v>
+        <v>258.8</v>
       </c>
       <c r="D62" s="3">
-        <v>258.8</v>
+        <v>242.8</v>
       </c>
       <c r="E62" s="3">
-        <v>242.8</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="F62" s="3">
-        <v>143.80000000000001</v>
-      </c>
-      <c r="G62" s="3">
         <v>29.5</v>
       </c>
+      <c r="G62">
+        <v>21</v>
+      </c>
       <c r="H62">
-        <v>21</v>
-      </c>
-      <c r="I62">
         <v>7.0000000000000098</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" s="3">
-        <v>226158</v>
+        <v>1200</v>
       </c>
       <c r="C63" s="3">
-        <v>1200</v>
+        <v>262.10000000000002</v>
       </c>
       <c r="D63" s="3">
-        <v>262.10000000000002</v>
+        <v>246.6</v>
       </c>
       <c r="E63" s="3">
-        <v>246.6</v>
+        <v>146</v>
       </c>
       <c r="F63" s="3">
-        <v>146</v>
-      </c>
-      <c r="G63" s="3">
         <v>30</v>
       </c>
+      <c r="G63">
+        <v>21.3</v>
+      </c>
       <c r="H63">
-        <v>21.3</v>
-      </c>
-      <c r="I63">
         <v>7.1</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>248773</v>
+        <v>1220</v>
       </c>
       <c r="C64" s="3">
-        <v>1220</v>
+        <v>265.39999999999998</v>
       </c>
       <c r="D64" s="3">
-        <v>265.39999999999998</v>
+        <v>250.4</v>
       </c>
       <c r="E64" s="3">
-        <v>250.4</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="F64" s="3">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="G64" s="3">
         <v>30.5</v>
       </c>
+      <c r="G64">
+        <v>21.6</v>
+      </c>
       <c r="H64">
-        <v>21.6</v>
-      </c>
-      <c r="I64">
         <v>7.2000000000000099</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:8">
       <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="3">
-        <v>273650</v>
+        <v>1240</v>
       </c>
       <c r="C65" s="3">
-        <v>1240</v>
+        <v>268.7</v>
       </c>
       <c r="D65" s="3">
-        <v>268.7</v>
+        <v>254.2</v>
       </c>
       <c r="E65" s="3">
-        <v>254.2</v>
+        <v>150.4</v>
       </c>
       <c r="F65" s="3">
-        <v>150.4</v>
-      </c>
-      <c r="G65" s="3">
         <v>31</v>
       </c>
+      <c r="G65">
+        <v>21.9</v>
+      </c>
       <c r="H65">
-        <v>21.9</v>
-      </c>
-      <c r="I65">
         <v>7.3000000000000096</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>301015</v>
+        <v>1260</v>
       </c>
       <c r="C66" s="3">
-        <v>1260</v>
+        <v>272</v>
       </c>
       <c r="D66" s="3">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="E66" s="3">
-        <v>258</v>
+        <v>152.6</v>
       </c>
       <c r="F66" s="3">
-        <v>152.6</v>
-      </c>
-      <c r="G66" s="3">
         <v>31.5</v>
       </c>
+      <c r="G66">
+        <v>22.2</v>
+      </c>
       <c r="H66">
-        <v>22.2</v>
-      </c>
-      <c r="I66">
         <v>7.4000000000000101</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" s="3">
-        <v>331116</v>
+        <v>1280</v>
       </c>
       <c r="C67" s="3">
-        <v>1280</v>
+        <v>275.3</v>
       </c>
       <c r="D67" s="3">
-        <v>275.3</v>
+        <v>261.8</v>
       </c>
       <c r="E67" s="3">
-        <v>261.8</v>
+        <v>154.80000000000001</v>
       </c>
       <c r="F67" s="3">
-        <v>154.80000000000001</v>
-      </c>
-      <c r="G67" s="3">
         <v>32</v>
       </c>
+      <c r="G67">
+        <v>22.5</v>
+      </c>
       <c r="H67">
-        <v>22.5</v>
-      </c>
-      <c r="I67">
         <v>7.5000000000000098</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>364227</v>
+        <v>1300</v>
       </c>
       <c r="C68" s="3">
-        <v>1300</v>
+        <v>278.60000000000002</v>
       </c>
       <c r="D68" s="3">
-        <v>278.60000000000002</v>
+        <v>265.60000000000002</v>
       </c>
       <c r="E68" s="3">
-        <v>265.60000000000002</v>
+        <v>157</v>
       </c>
       <c r="F68" s="3">
-        <v>157</v>
-      </c>
-      <c r="G68" s="3">
         <v>32.5</v>
       </c>
+      <c r="G68">
+        <v>22.8</v>
+      </c>
       <c r="H68">
-        <v>22.8</v>
-      </c>
-      <c r="I68">
         <v>7.6000000000000103</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:8">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="3">
-        <v>400649</v>
+        <v>1320</v>
       </c>
       <c r="C69" s="3">
-        <v>1320</v>
+        <v>281.89999999999998</v>
       </c>
       <c r="D69" s="3">
-        <v>281.89999999999998</v>
+        <v>269.39999999999998</v>
       </c>
       <c r="E69" s="3">
-        <v>269.39999999999998</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="F69" s="3">
-        <v>159.19999999999999</v>
-      </c>
-      <c r="G69" s="3">
         <v>33</v>
       </c>
+      <c r="G69">
+        <v>23.1</v>
+      </c>
       <c r="H69">
-        <v>23.1</v>
-      </c>
-      <c r="I69">
         <v>7.7000000000000099</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>440713</v>
+        <v>1340</v>
       </c>
       <c r="C70" s="3">
-        <v>1340</v>
+        <v>285.2</v>
       </c>
       <c r="D70" s="3">
-        <v>285.2</v>
+        <v>273.2</v>
       </c>
       <c r="E70" s="3">
-        <v>273.2</v>
+        <v>161.4</v>
       </c>
       <c r="F70" s="3">
-        <v>161.4</v>
-      </c>
-      <c r="G70" s="3">
         <v>33.5</v>
       </c>
+      <c r="G70">
+        <v>23.4</v>
+      </c>
       <c r="H70">
-        <v>23.4</v>
-      </c>
-      <c r="I70">
         <v>7.8000000000000096</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" s="3">
-        <v>484784</v>
+        <v>1360</v>
       </c>
       <c r="C71" s="3">
-        <v>1360</v>
+        <v>288.5</v>
       </c>
       <c r="D71" s="3">
-        <v>288.5</v>
+        <v>277</v>
       </c>
       <c r="E71" s="3">
-        <v>277</v>
+        <v>163.6</v>
       </c>
       <c r="F71" s="3">
-        <v>163.6</v>
-      </c>
-      <c r="G71" s="3">
         <v>34</v>
       </c>
+      <c r="G71">
+        <v>23.7</v>
+      </c>
       <c r="H71">
-        <v>23.7</v>
-      </c>
-      <c r="I71">
         <v>7.9000000000000101</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:8">
       <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>533262</v>
+        <v>1380</v>
       </c>
       <c r="C72" s="3">
-        <v>1380</v>
+        <v>291.8</v>
       </c>
       <c r="D72" s="3">
-        <v>291.8</v>
+        <v>280.8</v>
       </c>
       <c r="E72" s="3">
-        <v>280.8</v>
+        <v>165.8</v>
       </c>
       <c r="F72" s="3">
-        <v>165.8</v>
-      </c>
-      <c r="G72" s="3">
         <v>34.5</v>
       </c>
+      <c r="G72">
+        <v>24</v>
+      </c>
       <c r="H72">
-        <v>24</v>
-      </c>
-      <c r="I72">
         <v>8.0000000000000107</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" s="3">
-        <v>586588</v>
+        <v>1400</v>
       </c>
       <c r="C73" s="3">
-        <v>1400</v>
+        <v>295.10000000000002</v>
       </c>
       <c r="D73" s="3">
-        <v>295.10000000000002</v>
+        <v>284.60000000000002</v>
       </c>
       <c r="E73" s="3">
-        <v>284.60000000000002</v>
+        <v>168</v>
       </c>
       <c r="F73" s="3">
-        <v>168</v>
-      </c>
-      <c r="G73" s="3">
         <v>35</v>
       </c>
+      <c r="G73">
+        <v>24.3</v>
+      </c>
       <c r="H73">
-        <v>24.3</v>
-      </c>
-      <c r="I73">
         <v>8.1000000000000103</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>645246</v>
+        <v>1420</v>
       </c>
       <c r="C74" s="3">
-        <v>1420</v>
+        <v>298.39999999999998</v>
       </c>
       <c r="D74" s="3">
-        <v>298.39999999999998</v>
+        <v>288.39999999999998</v>
       </c>
       <c r="E74" s="3">
-        <v>288.39999999999998</v>
+        <v>170.2</v>
       </c>
       <c r="F74" s="3">
-        <v>170.2</v>
-      </c>
-      <c r="G74" s="3">
         <v>35.5</v>
       </c>
+      <c r="G74">
+        <v>24.6</v>
+      </c>
       <c r="H74">
-        <v>24.6</v>
-      </c>
-      <c r="I74">
         <v>8.2000000000000099</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:8">
       <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="3">
-        <v>709770</v>
+        <v>1440</v>
       </c>
       <c r="C75" s="3">
-        <v>1440</v>
+        <v>301.7</v>
       </c>
       <c r="D75" s="3">
-        <v>301.7</v>
+        <v>292.2</v>
       </c>
       <c r="E75" s="3">
-        <v>292.2</v>
+        <v>172.4</v>
       </c>
       <c r="F75" s="3">
-        <v>172.4</v>
-      </c>
-      <c r="G75" s="3">
         <v>36</v>
       </c>
+      <c r="G75">
+        <v>24.9</v>
+      </c>
       <c r="H75">
-        <v>24.9</v>
-      </c>
-      <c r="I75">
         <v>8.3000000000000096</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>780747</v>
+        <v>1460</v>
       </c>
       <c r="C76" s="3">
-        <v>1460</v>
+        <v>305</v>
       </c>
       <c r="D76" s="3">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E76" s="3">
-        <v>296</v>
+        <v>174.6</v>
       </c>
       <c r="F76" s="3">
-        <v>174.6</v>
-      </c>
-      <c r="G76" s="3">
         <v>36.5</v>
       </c>
+      <c r="G76">
+        <v>25.2</v>
+      </c>
       <c r="H76">
-        <v>25.2</v>
-      </c>
-      <c r="I76">
         <v>8.4000000000000092</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" s="3">
-        <v>858821</v>
+        <v>1480</v>
       </c>
       <c r="C77" s="3">
-        <v>1480</v>
+        <v>308.3</v>
       </c>
       <c r="D77" s="3">
-        <v>308.3</v>
+        <v>299.8</v>
       </c>
       <c r="E77" s="3">
-        <v>299.8</v>
+        <v>176.8</v>
       </c>
       <c r="F77" s="3">
-        <v>176.8</v>
-      </c>
-      <c r="G77" s="3">
         <v>37</v>
       </c>
+      <c r="G77">
+        <v>25.5</v>
+      </c>
       <c r="H77">
-        <v>25.5</v>
-      </c>
-      <c r="I77">
         <v>8.5000000000000107</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:8">
       <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>944703</v>
+        <v>1500</v>
       </c>
       <c r="C78" s="3">
-        <v>1500</v>
+        <v>311.60000000000002</v>
       </c>
       <c r="D78" s="3">
-        <v>311.60000000000002</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="E78" s="3">
-        <v>303.60000000000002</v>
+        <v>179</v>
       </c>
       <c r="F78" s="3">
-        <v>179</v>
-      </c>
-      <c r="G78" s="3">
         <v>37.5</v>
       </c>
+      <c r="G78">
+        <v>25.8</v>
+      </c>
       <c r="H78">
-        <v>25.8</v>
-      </c>
-      <c r="I78">
         <v>8.6000000000000103</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" s="3">
-        <v>1039173</v>
+        <v>1520</v>
       </c>
       <c r="C79" s="3">
-        <v>1520</v>
+        <v>314.89999999999998</v>
       </c>
       <c r="D79" s="3">
-        <v>314.89999999999998</v>
+        <v>307.39999999999998</v>
       </c>
       <c r="E79" s="3">
-        <v>307.39999999999998</v>
+        <v>181.2</v>
       </c>
       <c r="F79" s="3">
-        <v>181.2</v>
-      </c>
-      <c r="G79" s="3">
         <v>38</v>
       </c>
+      <c r="G79">
+        <v>26.1</v>
+      </c>
       <c r="H79">
-        <v>26.1</v>
-      </c>
-      <c r="I79">
         <v>8.7000000000000099</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>1143090</v>
+        <v>1540</v>
       </c>
       <c r="C80" s="3">
-        <v>1540</v>
+        <v>318.2</v>
       </c>
       <c r="D80" s="3">
-        <v>318.2</v>
+        <v>311.2</v>
       </c>
       <c r="E80" s="3">
-        <v>311.2</v>
+        <v>183.4</v>
       </c>
       <c r="F80" s="3">
-        <v>183.4</v>
-      </c>
-      <c r="G80" s="3">
         <v>38.5</v>
       </c>
+      <c r="G80">
+        <v>26.4</v>
+      </c>
       <c r="H80">
-        <v>26.4</v>
-      </c>
-      <c r="I80">
         <v>8.8000000000000096</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:8">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="3">
-        <v>1257399</v>
+        <v>1560</v>
       </c>
       <c r="C81" s="3">
-        <v>1560</v>
+        <v>321.5</v>
       </c>
       <c r="D81" s="3">
-        <v>321.5</v>
+        <v>315</v>
       </c>
       <c r="E81" s="3">
-        <v>315</v>
+        <v>185.6</v>
       </c>
       <c r="F81" s="3">
-        <v>185.6</v>
-      </c>
-      <c r="G81" s="3">
         <v>39</v>
       </c>
+      <c r="G81">
+        <v>26.7</v>
+      </c>
       <c r="H81">
-        <v>26.7</v>
-      </c>
-      <c r="I81">
         <v>8.9000000000000092</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>1383138</v>
+        <v>1580</v>
       </c>
       <c r="C82" s="3">
-        <v>1580</v>
+        <v>324.8</v>
       </c>
       <c r="D82" s="3">
-        <v>324.8</v>
+        <v>318.8</v>
       </c>
       <c r="E82" s="3">
-        <v>318.8</v>
+        <v>187.8</v>
       </c>
       <c r="F82" s="3">
-        <v>187.8</v>
-      </c>
-      <c r="G82" s="3">
         <v>39.5</v>
       </c>
+      <c r="G82">
+        <v>27</v>
+      </c>
       <c r="H82">
-        <v>27</v>
-      </c>
-      <c r="I82">
         <v>9.0000000000000107</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="3">
-        <v>1521451</v>
+        <v>1600</v>
       </c>
       <c r="C83" s="3">
-        <v>1600</v>
+        <v>328.1</v>
       </c>
       <c r="D83" s="3">
-        <v>328.1</v>
+        <v>322.60000000000002</v>
       </c>
       <c r="E83" s="3">
-        <v>322.60000000000002</v>
+        <v>190</v>
       </c>
       <c r="F83" s="3">
-        <v>190</v>
-      </c>
-      <c r="G83" s="3">
         <v>40</v>
       </c>
+      <c r="G83">
+        <v>27.3</v>
+      </c>
       <c r="H83">
-        <v>27.3</v>
-      </c>
-      <c r="I83">
         <v>9.1000000000000103</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:8">
       <c r="A84" s="4">
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>1673596</v>
+        <v>1620</v>
       </c>
       <c r="C84" s="3">
-        <v>1620</v>
+        <v>331.4</v>
       </c>
       <c r="D84" s="3">
-        <v>331.4</v>
+        <v>326.39999999999998</v>
       </c>
       <c r="E84" s="3">
-        <v>326.39999999999998</v>
+        <v>192.2</v>
       </c>
       <c r="F84" s="3">
-        <v>192.2</v>
-      </c>
-      <c r="G84" s="3">
         <v>40.5</v>
       </c>
+      <c r="G84">
+        <v>27.6</v>
+      </c>
       <c r="H84">
-        <v>27.6</v>
-      </c>
-      <c r="I84">
         <v>9.2000000000000099</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" s="3">
-        <v>1840955</v>
+        <v>1640</v>
       </c>
       <c r="C85" s="3">
-        <v>1640</v>
+        <v>334.7</v>
       </c>
       <c r="D85" s="3">
-        <v>334.7</v>
+        <v>330.2</v>
       </c>
       <c r="E85" s="3">
-        <v>330.2</v>
+        <v>194.4</v>
       </c>
       <c r="F85" s="3">
-        <v>194.4</v>
-      </c>
-      <c r="G85" s="3">
         <v>41</v>
       </c>
+      <c r="G85">
+        <v>27.9</v>
+      </c>
       <c r="H85">
-        <v>27.9</v>
-      </c>
-      <c r="I85">
         <v>9.3000000000000096</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>2025050</v>
+        <v>1660</v>
       </c>
       <c r="C86" s="3">
-        <v>1660</v>
+        <v>338</v>
       </c>
       <c r="D86" s="3">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E86" s="3">
-        <v>334</v>
+        <v>196.6</v>
       </c>
       <c r="F86" s="3">
-        <v>196.6</v>
-      </c>
-      <c r="G86" s="3">
         <v>41.5</v>
       </c>
+      <c r="G86">
+        <v>28.2</v>
+      </c>
       <c r="H86">
-        <v>28.2</v>
-      </c>
-      <c r="I86">
         <v>9.4000000000000092</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:8">
       <c r="A87" s="4">
         <v>86</v>
       </c>
       <c r="B87" s="3">
-        <v>2227555</v>
+        <v>1680</v>
       </c>
       <c r="C87" s="3">
-        <v>1680</v>
+        <v>341.3</v>
       </c>
       <c r="D87" s="3">
-        <v>341.3</v>
+        <v>337.8</v>
       </c>
       <c r="E87" s="3">
-        <v>337.8</v>
+        <v>198.8</v>
       </c>
       <c r="F87" s="3">
-        <v>198.8</v>
-      </c>
-      <c r="G87" s="3">
         <v>42</v>
       </c>
+      <c r="G87">
+        <v>28.5</v>
+      </c>
       <c r="H87">
-        <v>28.5</v>
-      </c>
-      <c r="I87">
         <v>9.5000000000000107</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>2450310</v>
+        <v>1700</v>
       </c>
       <c r="C88" s="3">
-        <v>1700</v>
+        <v>344.6</v>
       </c>
       <c r="D88" s="3">
-        <v>344.6</v>
+        <v>341.6</v>
       </c>
       <c r="E88" s="3">
-        <v>341.6</v>
+        <v>201</v>
       </c>
       <c r="F88" s="3">
-        <v>201</v>
-      </c>
-      <c r="G88" s="3">
         <v>42.5</v>
       </c>
+      <c r="G88">
+        <v>28.8</v>
+      </c>
       <c r="H88">
-        <v>28.8</v>
-      </c>
-      <c r="I88">
         <v>9.6000000000000103</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" s="3">
-        <v>2695341</v>
+        <v>1720</v>
       </c>
       <c r="C89" s="3">
-        <v>1720</v>
+        <v>347.9</v>
       </c>
       <c r="D89" s="3">
-        <v>347.9</v>
+        <v>345.4</v>
       </c>
       <c r="E89" s="3">
-        <v>345.4</v>
+        <v>203.2</v>
       </c>
       <c r="F89" s="3">
-        <v>203.2</v>
-      </c>
-      <c r="G89" s="3">
         <v>43</v>
       </c>
+      <c r="G89">
+        <v>29.1</v>
+      </c>
       <c r="H89">
-        <v>29.1</v>
-      </c>
-      <c r="I89">
         <v>9.7000000000000099</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>2964875</v>
+        <v>1740</v>
       </c>
       <c r="C90" s="3">
-        <v>1740</v>
+        <v>351.2</v>
       </c>
       <c r="D90" s="3">
-        <v>351.2</v>
+        <v>349.2</v>
       </c>
       <c r="E90" s="3">
-        <v>349.2</v>
+        <v>205.4</v>
       </c>
       <c r="F90" s="3">
-        <v>205.4</v>
-      </c>
-      <c r="G90" s="3">
         <v>43.5</v>
       </c>
+      <c r="G90">
+        <v>29.4</v>
+      </c>
       <c r="H90">
-        <v>29.4</v>
-      </c>
-      <c r="I90">
         <v>9.8000000000000096</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:8">
       <c r="A91" s="4">
         <v>90</v>
       </c>
       <c r="B91" s="3">
-        <v>3261362</v>
+        <v>1760</v>
       </c>
       <c r="C91" s="3">
-        <v>1760</v>
+        <v>354.5</v>
       </c>
       <c r="D91" s="3">
-        <v>354.5</v>
+        <v>353</v>
       </c>
       <c r="E91" s="3">
-        <v>353</v>
+        <v>207.6</v>
       </c>
       <c r="F91" s="3">
-        <v>207.6</v>
-      </c>
-      <c r="G91" s="3">
         <v>44</v>
       </c>
+      <c r="G91">
+        <v>29.7</v>
+      </c>
       <c r="H91">
-        <v>29.7</v>
-      </c>
-      <c r="I91">
         <v>9.9000000000000092</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:8">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>3587498</v>
+        <v>1780</v>
       </c>
       <c r="C92" s="3">
-        <v>1780</v>
+        <v>357.8</v>
       </c>
       <c r="D92" s="3">
-        <v>357.8</v>
+        <v>356.8</v>
       </c>
       <c r="E92" s="3">
-        <v>356.8</v>
+        <v>209.8</v>
       </c>
       <c r="F92" s="3">
-        <v>209.8</v>
-      </c>
-      <c r="G92" s="3">
         <v>44.5</v>
       </c>
+      <c r="G92">
+        <v>30</v>
+      </c>
       <c r="H92">
-        <v>30</v>
-      </c>
-      <c r="I92">
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:8">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" s="3">
-        <v>3946247</v>
+        <v>1800</v>
       </c>
       <c r="C93" s="3">
-        <v>1800</v>
+        <v>361.1</v>
       </c>
       <c r="D93" s="3">
-        <v>361.1</v>
+        <v>360.6</v>
       </c>
       <c r="E93" s="3">
-        <v>360.6</v>
+        <v>212</v>
       </c>
       <c r="F93" s="3">
-        <v>212</v>
-      </c>
-      <c r="G93" s="3">
         <v>45</v>
       </c>
+      <c r="G93">
+        <v>30.3</v>
+      </c>
       <c r="H93">
-        <v>30.3</v>
-      </c>
-      <c r="I93">
         <v>10.1</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:8">
       <c r="A94" s="4">
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>4340871</v>
+        <v>1820</v>
       </c>
       <c r="C94" s="3">
-        <v>1820</v>
+        <v>364.4</v>
       </c>
       <c r="D94" s="3">
         <v>364.4</v>
       </c>
       <c r="E94" s="3">
-        <v>364.4</v>
+        <v>214.2</v>
       </c>
       <c r="F94" s="3">
-        <v>214.2</v>
-      </c>
-      <c r="G94" s="3">
         <v>45.5</v>
       </c>
+      <c r="G94">
+        <v>30.6</v>
+      </c>
       <c r="H94">
-        <v>30.6</v>
-      </c>
-      <c r="I94">
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" s="3">
-        <v>4774958</v>
+        <v>1840</v>
       </c>
       <c r="C95" s="3">
-        <v>1840</v>
+        <v>367.7</v>
       </c>
       <c r="D95" s="3">
-        <v>367.7</v>
+        <v>368.2</v>
       </c>
       <c r="E95" s="3">
-        <v>368.2</v>
+        <v>216.4</v>
       </c>
       <c r="F95" s="3">
-        <v>216.4</v>
-      </c>
-      <c r="G95" s="3">
         <v>46</v>
       </c>
+      <c r="G95">
+        <v>30.9</v>
+      </c>
       <c r="H95">
-        <v>30.9</v>
-      </c>
-      <c r="I95">
         <v>10.3</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:8">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>5252453</v>
+        <v>1860</v>
       </c>
       <c r="C96" s="3">
-        <v>1860</v>
+        <v>371</v>
       </c>
       <c r="D96" s="3">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E96" s="3">
-        <v>372</v>
+        <v>218.6</v>
       </c>
       <c r="F96" s="3">
-        <v>218.6</v>
-      </c>
-      <c r="G96" s="3">
         <v>46.5</v>
       </c>
+      <c r="G96">
+        <v>31.2</v>
+      </c>
       <c r="H96">
-        <v>31.2</v>
-      </c>
-      <c r="I96">
         <v>10.4</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:8">
       <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="3">
-        <v>5777698</v>
+        <v>1880</v>
       </c>
       <c r="C97" s="3">
-        <v>1880</v>
+        <v>374.3</v>
       </c>
       <c r="D97" s="3">
-        <v>374.3</v>
+        <v>375.8</v>
       </c>
       <c r="E97" s="3">
-        <v>375.8</v>
+        <v>220.8</v>
       </c>
       <c r="F97" s="3">
-        <v>220.8</v>
-      </c>
-      <c r="G97" s="3">
         <v>47</v>
       </c>
+      <c r="G97">
+        <v>31.5</v>
+      </c>
       <c r="H97">
-        <v>31.5</v>
-      </c>
-      <c r="I97">
         <v>10.5</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>6355467</v>
+        <v>1900</v>
       </c>
       <c r="C98" s="3">
-        <v>1900</v>
+        <v>377.6</v>
       </c>
       <c r="D98" s="3">
-        <v>377.6</v>
+        <v>379.6</v>
       </c>
       <c r="E98" s="3">
-        <v>379.6</v>
+        <v>223</v>
       </c>
       <c r="F98" s="3">
-        <v>223</v>
-      </c>
-      <c r="G98" s="3">
         <v>47.5</v>
       </c>
+      <c r="G98">
+        <v>31.8</v>
+      </c>
       <c r="H98">
-        <v>31.8</v>
-      </c>
-      <c r="I98">
         <v>10.6</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" s="3">
-        <v>6991013</v>
+        <v>1920</v>
       </c>
       <c r="C99" s="3">
-        <v>1920</v>
+        <v>380.9</v>
       </c>
       <c r="D99" s="3">
-        <v>380.9</v>
+        <v>383.4</v>
       </c>
       <c r="E99" s="3">
-        <v>383.4</v>
+        <v>225.2</v>
       </c>
       <c r="F99" s="3">
-        <v>225.2</v>
-      </c>
-      <c r="G99" s="3">
         <v>48</v>
       </c>
+      <c r="G99">
+        <v>32.1</v>
+      </c>
       <c r="H99">
-        <v>32.1</v>
-      </c>
-      <c r="I99">
         <v>10.7</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:8">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>7690114</v>
+        <v>1940</v>
       </c>
       <c r="C100" s="3">
-        <v>1940</v>
+        <v>384.2</v>
       </c>
       <c r="D100" s="3">
-        <v>384.2</v>
+        <v>387.2</v>
       </c>
       <c r="E100" s="3">
-        <v>387.2</v>
+        <v>227.4</v>
       </c>
       <c r="F100" s="3">
-        <v>227.4</v>
-      </c>
-      <c r="G100" s="3">
         <v>48.5</v>
       </c>
+      <c r="G100">
+        <v>32.4</v>
+      </c>
       <c r="H100">
-        <v>32.4</v>
-      </c>
-      <c r="I100">
         <v>10.8</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" s="3">
-        <v>8459125</v>
+        <v>1960</v>
       </c>
       <c r="C101" s="3">
-        <v>1960</v>
+        <v>387.5</v>
       </c>
       <c r="D101" s="3">
-        <v>387.5</v>
+        <v>391</v>
       </c>
       <c r="E101" s="3">
-        <v>391</v>
+        <v>229.6</v>
       </c>
       <c r="F101" s="3">
-        <v>229.6</v>
-      </c>
-      <c r="G101" s="3">
         <v>49</v>
       </c>
+      <c r="G101">
+        <v>32.700000000000003</v>
+      </c>
       <c r="H101">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="I101">
         <v>10.9</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" s="3">
-        <v>9305037</v>
+        <v>1980</v>
       </c>
       <c r="C102" s="3">
-        <v>1980</v>
+        <v>390.8</v>
       </c>
       <c r="D102" s="3">
-        <v>390.8</v>
+        <v>394.8</v>
       </c>
       <c r="E102" s="3">
-        <v>394.8</v>
+        <v>231.8</v>
       </c>
       <c r="F102" s="3">
-        <v>231.8</v>
-      </c>
-      <c r="G102" s="3">
         <v>49.5</v>
       </c>
+      <c r="G102">
+        <v>33</v>
+      </c>
       <c r="H102">
-        <v>33</v>
-      </c>
-      <c r="I102">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:8">
       <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="3">
-        <v>10235540</v>
+        <v>2000</v>
       </c>
       <c r="C103" s="3">
-        <v>2000</v>
+        <v>394.1</v>
       </c>
       <c r="D103" s="3">
-        <v>394.1</v>
+        <v>398.6</v>
       </c>
       <c r="E103" s="3">
-        <v>398.6</v>
+        <v>234</v>
       </c>
       <c r="F103" s="3">
-        <v>234</v>
-      </c>
-      <c r="G103" s="3">
         <v>50</v>
       </c>
+      <c r="G103">
+        <v>33.299999999999997</v>
+      </c>
       <c r="H103">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="I103">
         <v>11.1</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" s="3">
-        <v>11259094</v>
+        <v>2020</v>
       </c>
       <c r="C104" s="3">
-        <v>2020</v>
+        <v>397.4</v>
       </c>
       <c r="D104" s="3">
-        <v>397.4</v>
+        <v>402.4</v>
       </c>
       <c r="E104" s="3">
-        <v>402.4</v>
+        <v>236.2</v>
       </c>
       <c r="F104" s="3">
-        <v>236.2</v>
-      </c>
-      <c r="G104" s="3">
         <v>50.5</v>
       </c>
+      <c r="G104">
+        <v>33.6</v>
+      </c>
       <c r="H104">
-        <v>33.6</v>
-      </c>
-      <c r="I104">
         <v>11.2</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" s="3">
-        <v>12385003</v>
+        <v>2040</v>
       </c>
       <c r="C105" s="3">
-        <v>2040</v>
+        <v>400.7</v>
       </c>
       <c r="D105" s="3">
-        <v>400.7</v>
+        <v>406.2</v>
       </c>
       <c r="E105" s="3">
-        <v>406.2</v>
+        <v>238.4</v>
       </c>
       <c r="F105" s="3">
-        <v>238.4</v>
-      </c>
-      <c r="G105" s="3">
         <v>51</v>
       </c>
+      <c r="G105">
+        <v>33.9</v>
+      </c>
       <c r="H105">
-        <v>33.9</v>
-      </c>
-      <c r="I105">
         <v>11.3</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:8">
       <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="3">
-        <v>13623503</v>
+        <v>2060</v>
       </c>
       <c r="C106" s="3">
-        <v>2060</v>
+        <v>404</v>
       </c>
       <c r="D106" s="3">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E106" s="3">
-        <v>410</v>
+        <v>240.6</v>
       </c>
       <c r="F106" s="3">
-        <v>240.6</v>
-      </c>
-      <c r="G106" s="3">
         <v>51.5</v>
       </c>
+      <c r="G106">
+        <v>34.200000000000003</v>
+      </c>
       <c r="H106">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="I106">
         <v>11.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" s="3">
-        <v>14985853</v>
+        <v>2080</v>
       </c>
       <c r="C107" s="3">
-        <v>2080</v>
+        <v>407.3</v>
       </c>
       <c r="D107" s="3">
-        <v>407.3</v>
+        <v>413.8</v>
       </c>
       <c r="E107" s="3">
-        <v>413.8</v>
+        <v>242.8</v>
       </c>
       <c r="F107" s="3">
-        <v>242.8</v>
-      </c>
-      <c r="G107" s="3">
         <v>52</v>
       </c>
+      <c r="G107">
+        <v>34.5</v>
+      </c>
       <c r="H107">
-        <v>34.5</v>
-      </c>
-      <c r="I107">
         <v>11.5</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" s="3">
-        <v>16484438</v>
+        <v>2100</v>
       </c>
       <c r="C108" s="3">
-        <v>2100</v>
+        <v>410.6</v>
       </c>
       <c r="D108" s="3">
-        <v>410.6</v>
+        <v>417.6</v>
       </c>
       <c r="E108" s="3">
-        <v>417.6</v>
+        <v>245</v>
       </c>
       <c r="F108" s="3">
-        <v>245</v>
-      </c>
-      <c r="G108" s="3">
         <v>52.5</v>
       </c>
+      <c r="G108">
+        <v>34.799999999999997</v>
+      </c>
       <c r="H108">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="I108">
         <v>11.6</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:8">
       <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="3">
-        <v>18132881</v>
+        <v>2120</v>
       </c>
       <c r="C109" s="3">
-        <v>2120</v>
+        <v>413.9</v>
       </c>
       <c r="D109" s="3">
-        <v>413.9</v>
+        <v>421.4</v>
       </c>
       <c r="E109" s="3">
-        <v>421.4</v>
+        <v>247.2</v>
       </c>
       <c r="F109" s="3">
-        <v>247.2</v>
-      </c>
-      <c r="G109" s="3">
         <v>53</v>
       </c>
+      <c r="G109">
+        <v>35.1</v>
+      </c>
       <c r="H109">
-        <v>35.1</v>
-      </c>
-      <c r="I109">
         <v>11.7</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" s="3">
-        <v>19946169</v>
+        <v>2140</v>
       </c>
       <c r="C110" s="3">
-        <v>2140</v>
+        <v>417.2</v>
       </c>
       <c r="D110" s="3">
-        <v>417.2</v>
+        <v>425.2</v>
       </c>
       <c r="E110" s="3">
-        <v>425.2</v>
+        <v>249.4</v>
       </c>
       <c r="F110" s="3">
-        <v>249.4</v>
-      </c>
-      <c r="G110" s="3">
         <v>53.5</v>
       </c>
+      <c r="G110">
+        <v>35.4</v>
+      </c>
       <c r="H110">
-        <v>35.4</v>
-      </c>
-      <c r="I110">
         <v>11.8</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" s="3">
-        <v>21940785</v>
+        <v>2160</v>
       </c>
       <c r="C111" s="3">
-        <v>2160</v>
+        <v>420.5</v>
       </c>
       <c r="D111" s="3">
-        <v>420.5</v>
+        <v>429</v>
       </c>
       <c r="E111" s="3">
-        <v>429</v>
+        <v>251.6</v>
       </c>
       <c r="F111" s="3">
-        <v>251.6</v>
-      </c>
-      <c r="G111" s="3">
         <v>54</v>
       </c>
+      <c r="G111">
+        <v>35.700000000000003</v>
+      </c>
       <c r="H111">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="I111">
         <v>11.9</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" s="3">
-        <v>24134863</v>
+        <v>2180</v>
       </c>
       <c r="C112" s="3">
-        <v>2180</v>
+        <v>423.8</v>
       </c>
       <c r="D112" s="3">
-        <v>423.8</v>
+        <v>432.8</v>
       </c>
       <c r="E112" s="3">
-        <v>432.8</v>
+        <v>253.8</v>
       </c>
       <c r="F112" s="3">
-        <v>253.8</v>
-      </c>
-      <c r="G112" s="3">
         <v>54.5</v>
       </c>
+      <c r="G112">
+        <v>36</v>
+      </c>
       <c r="H112">
-        <v>36</v>
-      </c>
-      <c r="I112">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:8">
       <c r="A113" s="4">
         <v>112</v>
       </c>
       <c r="B113" s="3">
-        <v>26548349</v>
+        <v>2200</v>
       </c>
       <c r="C113" s="3">
-        <v>2200</v>
+        <v>427.1</v>
       </c>
       <c r="D113" s="3">
-        <v>427.1</v>
+        <v>436.6</v>
       </c>
       <c r="E113" s="3">
-        <v>436.6</v>
+        <v>256</v>
       </c>
       <c r="F113" s="3">
-        <v>256</v>
-      </c>
-      <c r="G113" s="3">
         <v>55</v>
       </c>
+      <c r="G113">
+        <v>36.299999999999997</v>
+      </c>
       <c r="H113">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="I113">
         <v>12.1</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" s="3">
-        <v>29203183</v>
+        <v>2220</v>
       </c>
       <c r="C114" s="3">
-        <v>2220</v>
+        <v>430.4</v>
       </c>
       <c r="D114" s="3">
-        <v>430.4</v>
+        <v>440.4</v>
       </c>
       <c r="E114" s="3">
-        <v>440.4</v>
+        <v>258.2</v>
       </c>
       <c r="F114" s="3">
-        <v>258.2</v>
-      </c>
-      <c r="G114" s="3">
         <v>55.5</v>
       </c>
+      <c r="G114">
+        <v>36.6</v>
+      </c>
       <c r="H114">
-        <v>36.6</v>
-      </c>
-      <c r="I114">
         <v>12.2</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" s="3">
-        <v>32123501</v>
+        <v>2240</v>
       </c>
       <c r="C115" s="3">
-        <v>2240</v>
+        <v>433.7</v>
       </c>
       <c r="D115" s="3">
-        <v>433.7</v>
+        <v>444.2</v>
       </c>
       <c r="E115" s="3">
-        <v>444.2</v>
+        <v>260.39999999999998</v>
       </c>
       <c r="F115" s="3">
-        <v>260.39999999999998</v>
-      </c>
-      <c r="G115" s="3">
         <v>56</v>
       </c>
+      <c r="G115">
+        <v>36.9</v>
+      </c>
       <c r="H115">
-        <v>36.9</v>
-      </c>
-      <c r="I115">
         <v>12.3</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:8">
       <c r="A116" s="4">
         <v>115</v>
       </c>
       <c r="B116" s="3">
-        <v>35335851</v>
+        <v>2260</v>
       </c>
       <c r="C116" s="3">
-        <v>2260</v>
+        <v>437</v>
       </c>
       <c r="D116" s="3">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="E116" s="3">
-        <v>448</v>
+        <v>262.60000000000002</v>
       </c>
       <c r="F116" s="3">
-        <v>262.60000000000002</v>
-      </c>
-      <c r="G116" s="3">
         <v>56.5</v>
       </c>
+      <c r="G116">
+        <v>37.200000000000003</v>
+      </c>
       <c r="H116">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="I116">
         <v>12.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>38869436</v>
+        <v>2280</v>
       </c>
       <c r="C117" s="3">
-        <v>2280</v>
+        <v>440.3</v>
       </c>
       <c r="D117" s="3">
-        <v>440.3</v>
+        <v>451.8</v>
       </c>
       <c r="E117" s="3">
-        <v>451.8</v>
+        <v>264.8</v>
       </c>
       <c r="F117" s="3">
-        <v>264.8</v>
-      </c>
-      <c r="G117" s="3">
         <v>57</v>
       </c>
+      <c r="G117">
+        <v>37.5</v>
+      </c>
       <c r="H117">
-        <v>37.5</v>
-      </c>
-      <c r="I117">
         <v>12.5</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" s="3">
-        <v>42756379</v>
+        <v>2300</v>
       </c>
       <c r="C118" s="3">
-        <v>2300</v>
+        <v>443.6</v>
       </c>
       <c r="D118" s="3">
-        <v>443.6</v>
+        <v>455.6</v>
       </c>
       <c r="E118" s="3">
-        <v>455.6</v>
+        <v>267</v>
       </c>
       <c r="F118" s="3">
-        <v>267</v>
-      </c>
-      <c r="G118" s="3">
         <v>57.5</v>
       </c>
+      <c r="G118">
+        <v>37.799999999999997</v>
+      </c>
       <c r="H118">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I118">
         <v>12.6</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:8">
       <c r="A119" s="4">
         <v>118</v>
       </c>
       <c r="B119" s="3">
-        <v>47032016</v>
+        <v>2320</v>
       </c>
       <c r="C119" s="3">
-        <v>2320</v>
+        <v>446.9</v>
       </c>
       <c r="D119" s="3">
-        <v>446.9</v>
+        <v>459.4</v>
       </c>
       <c r="E119" s="3">
-        <v>459.4</v>
+        <v>269.2</v>
       </c>
       <c r="F119" s="3">
-        <v>269.2</v>
-      </c>
-      <c r="G119" s="3">
         <v>58</v>
       </c>
+      <c r="G119">
+        <v>38.1</v>
+      </c>
       <c r="H119">
-        <v>38.1</v>
-      </c>
-      <c r="I119">
         <v>12.7</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" s="3">
-        <v>51735217</v>
+        <v>2340</v>
       </c>
       <c r="C120" s="3">
-        <v>2340</v>
+        <v>450.2</v>
       </c>
       <c r="D120" s="3">
-        <v>450.2</v>
+        <v>463.2</v>
       </c>
       <c r="E120" s="3">
-        <v>463.2</v>
+        <v>271.39999999999998</v>
       </c>
       <c r="F120" s="3">
-        <v>271.39999999999998</v>
-      </c>
-      <c r="G120" s="3">
         <v>58.5</v>
       </c>
+      <c r="G120">
+        <v>38.4</v>
+      </c>
       <c r="H120">
-        <v>38.4</v>
-      </c>
-      <c r="I120">
         <v>12.8</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" s="3">
-        <v>56908738</v>
+        <v>2360</v>
       </c>
       <c r="C121" s="3">
-        <v>2360</v>
+        <v>453.5</v>
       </c>
       <c r="D121" s="3">
-        <v>453.5</v>
+        <v>467</v>
       </c>
       <c r="E121" s="3">
-        <v>467</v>
+        <v>273.60000000000002</v>
       </c>
       <c r="F121" s="3">
-        <v>273.60000000000002</v>
-      </c>
-      <c r="G121" s="3">
         <v>59</v>
       </c>
+      <c r="G121">
+        <v>38.700000000000003</v>
+      </c>
       <c r="H121">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="I121">
         <v>12.9</v>
       </c>
     </row>
@@ -3934,7 +4555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
@@ -4677,7 +5298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485FB2C5-1F28-4E73-BF64-811F13E99FFA}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
